--- a/engine/arcc_study/ARCC_Valuation_Model_01092026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_01092026_public.xlsx
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B29" s="26">
-        <f>Assumptions!$B$137-Assumptions!$B$138-Assumptions!$B$147</f>
+        <f>Assumptions!$B$137-Assumptions!$B$138-Assumptions!$B$149</f>
         <v/>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>Assumptions!$B$155</f>
+        <f>Assumptions!$B$157</f>
         <v/>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>Assumptions!$B$154</f>
+        <f>Assumptions!$B$156</f>
         <v/>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B18" s="40">
-        <f>Assumptions!$B$152</f>
+        <f>Assumptions!$B$154</f>
         <v/>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="B26" s="40">
-        <f>Assumptions!$B$153</f>
+        <f>Assumptions!$B$155</f>
         <v/>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>Assumptions!$B$150</f>
+        <f>Assumptions!$B$152</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B7" s="26">
-        <f>Assumptions!$B$151</f>
+        <f>Assumptions!$B$153</f>
         <v/>
       </c>
     </row>
@@ -2242,17 +2242,17 @@
     <row r="20">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>Cost of debt: currency composition as contracted (adopted) vs the pound-equivalent under uncovered interest parity</t>
+          <t>Cost of debt: the POUND-EQUIVALENT cost of a euro debt book (adopted) vs the contracted euro rate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>13.36%</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>7.89%</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>13.36%</t>
         </is>
       </c>
       <c r="D20" s="37">
@@ -2260,7 +2260,7 @@
         <v/>
       </c>
       <c r="E20" s="7" t="n">
-        <v>57.14477981467617</v>
+        <v>57.7228319891249</v>
       </c>
       <c r="F20" s="22">
         <f>E20/D20-1</f>
@@ -2288,7 +2288,7 @@
         <v/>
       </c>
       <c r="E21" s="7" t="n">
-        <v>63.39810772104384</v>
+        <v>63.64766794859425</v>
       </c>
       <c r="F21" s="22">
         <f>E21/D21-1</f>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USD 4.00/t</t>
+          <t>USD 3.23/t</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="E22" s="7" t="n">
-        <v>62.31581762408445</v>
+        <v>60.94880621186259</v>
       </c>
       <c r="F22" s="22">
         <f>E22/D22-1</f>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>Assumptions!$B$156</f>
+        <f>Assumptions!$B$158</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -2727,7 +2727,7 @@
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Assumptions!$B$157</f>
+        <f>Assumptions!$B$159</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -2755,7 +2755,7 @@
         <v/>
       </c>
       <c r="C7" s="18">
-        <f>Assumptions!$B$158</f>
+        <f>Assumptions!$B$160</f>
         <v/>
       </c>
       <c r="D7" s="34">
@@ -2783,7 +2783,7 @@
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>Assumptions!$B$159</f>
+        <f>Assumptions!$B$161</f>
         <v/>
       </c>
       <c r="D8" s="34">
@@ -2918,15 +2918,15 @@
         </is>
       </c>
       <c r="B17" s="34">
-        <f>((Assumptions!$B$151-15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$153-15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C17" s="34">
-        <f>(Assumptions!$B$151*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>(Assumptions!$B$153*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D17" s="34">
-        <f>((Assumptions!$B$151+15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$153+15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E17" s="22">
@@ -2941,15 +2941,15 @@
         </is>
       </c>
       <c r="B18" s="34">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$153-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$155-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C18" s="34">
-        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$153+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$155+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D18" s="34">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$153+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$155+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E18" s="22">
@@ -3415,102 +3415,102 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
-        <v>0.2419611926825002</v>
+        <v>0.2440290205561873</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>63.68177393875279</v>
+        <v>63.56777910220555</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>61.59359575968167</v>
+        <v>61.67670180841053</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>59.1408548220931</v>
+        <v>59.45547244152843</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>56.21894997058018</v>
+        <v>56.80936303635136</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>52.67903156448273</v>
+        <v>53.60357370919937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
-        <v>0.2569611926825002</v>
+        <v>0.2590290205561873</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>62.64701306522353</v>
+        <v>62.54799831980529</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>60.59895926648566</v>
+        <v>60.69321987406038</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>58.19334778902891</v>
+        <v>58.51462655782381</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>55.32758739048206</v>
+        <v>55.91930869011464</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>51.85568857864073</v>
+        <v>52.77505384388987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
-        <v>0.2719611926825002</v>
+        <v>0.2740290205561873</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>61.63891725772899</v>
+        <v>61.55438649124856</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59.62991881587249</v>
+        <v>59.73494091357318</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>57.27018114057266</v>
+        <v>57.5978490232327</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>54.4590693529025</v>
+        <v>55.0519710355419</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>51.05337790692043</v>
+        <v>51.96761312305255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
-        <v>0.2869611926825002</v>
+        <v>0.2890290205561873</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>60.65657237078804</v>
+        <v>60.58604874969223</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>58.68559741718179</v>
+        <v>58.80100359161905</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>56.37052152752652</v>
+        <v>56.70431788800833</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>53.61261449790975</v>
+        <v>54.20657504220203</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>50.27138117493181</v>
+        <v>51.18053335949985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
-        <v>0.3019611926825002</v>
+        <v>0.3040290205561873</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>59.69910370997297</v>
+        <v>59.64212877348545</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>57.76515591739703</v>
+        <v>57.89058366391598</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>55.49357154325129</v>
+        <v>55.83324658543686</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>52.78747515055075</v>
+        <v>53.38237902797042</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>49.50901095818169</v>
+        <v>50.41312724925825</v>
       </c>
     </row>
     <row r="12">
@@ -3550,102 +3550,102 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
-        <v>0.2419611926825002</v>
+        <v>0.2440290205561873</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>67.27793824599541</v>
+        <v>67.47870704511804</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>62.83132494096566</v>
+        <v>63.09261744959146</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>59.14100967416354</v>
+        <v>59.45547244152843</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>56.02535438535605</v>
+        <v>56.38719950096124</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>53.35669884588574</v>
+        <v>53.76124994257111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
-        <v>0.2569611926825002</v>
+        <v>0.2590290205561873</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>66.1684505130693</v>
+        <v>66.37836640150306</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>61.81036629928485</v>
+        <v>62.07948028951207</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>58.19350264109935</v>
+        <v>58.51462655782381</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>55.13984096087283</v>
+        <v>55.5073169521247</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>52.52426500914405</v>
+        <v>52.93352174313552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>0.2719611926825002</v>
+        <v>0.2740290205561873</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>65.0877410195933</v>
+        <v>65.30645788419812</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>60.81576011421328</v>
+        <v>61.09238904738929</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>57.2703359926431</v>
+        <v>57.5978490232327</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>54.27697027669902</v>
+        <v>54.64983562507949</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>51.71302091165267</v>
+        <v>52.12676906648366</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
-        <v>0.2869611926825002</v>
+        <v>0.2890290205561873</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>64.03481882481229</v>
+        <v>64.26200479502575</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>59.84660159736409</v>
+        <v>60.13045165579481</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>56.37067637959696</v>
+        <v>56.70431788800833</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>53.43596923979151</v>
+        <v>53.81399266176143</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>50.92224501484644</v>
+        <v>51.34027957097891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>0.3019611926825002</v>
+        <v>0.3040290205561873</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>63.00873588457741</v>
+        <v>63.24407263793392</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>58.90202505485783</v>
+        <v>59.19281451967432</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>55.49372639532173</v>
+        <v>55.83324658543686</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>52.616098041896</v>
+        <v>52.99905798434878</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>50.15124679172289</v>
+        <v>50.57337147085136</v>
       </c>
     </row>
     <row r="20">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>66.99388979580507</v>
+        <v>67.19832003681718</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>60.10910262517972</v>
+        <v>60.40085008307617</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>54.68916043151926</v>
+        <v>55.05241902978492</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>51.31929179150657</v>
+        <v>51.72828011624259</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>48.40610720477044</v>
+        <v>48.85537631226028</v>
       </c>
     </row>
     <row r="24">
@@ -3747,19 +3747,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>47.15219898772487</v>
+        <v>47.96904965852618</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>52.21119006414877</v>
+        <v>52.78344934087944</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>57.27018114057266</v>
+        <v>57.5978490232327</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>62.32917221699657</v>
+        <v>62.41224870558596</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>67.38816329342048</v>
+        <v>67.22664838793922</v>
       </c>
     </row>
     <row r="28">
@@ -3804,19 +3804,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>53.26876672060349</v>
+        <v>53.59643460326352</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>55.26947393058807</v>
+        <v>55.59714181324811</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>57.27018114057266</v>
+        <v>57.5978490232327</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>59.27088835055724</v>
+        <v>59.59855623321728</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>61.27159556054183</v>
+        <v>61.59926344320186</v>
       </c>
     </row>
     <row r="32">
@@ -3954,15 +3954,15 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>Assumptions!$B$166</f>
+        <f>Assumptions!$B$168</f>
         <v/>
       </c>
       <c r="C6" s="23">
-        <f>Assumptions!$B$167</f>
+        <f>Assumptions!$B$169</f>
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>Assumptions!$B$168</f>
+        <f>Assumptions!$B$170</f>
         <v/>
       </c>
       <c r="E6" s="40">
@@ -3985,15 +3985,15 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>Assumptions!$B$169</f>
+        <f>Assumptions!$B$171</f>
         <v/>
       </c>
       <c r="C7" s="23">
-        <f>Assumptions!$B$170</f>
+        <f>Assumptions!$B$172</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>Assumptions!$B$171</f>
+        <f>Assumptions!$B$173</f>
         <v/>
       </c>
       <c r="E7" s="40">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="B13" s="48">
-        <f>Assumptions!$B$161</f>
+        <f>Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="B14" s="48">
-        <f>Assumptions!$B$162</f>
+        <f>Assumptions!$B$164</f>
         <v/>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="B15" s="48">
-        <f>Assumptions!$B$163</f>
+        <f>Assumptions!$B$165</f>
         <v/>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B16" s="48">
-        <f>Assumptions!$B$164</f>
+        <f>Assumptions!$B$166</f>
         <v/>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="B17" s="48">
-        <f>Assumptions!$B$165</f>
+        <f>Assumptions!$B$167</f>
         <v/>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -5969,201 +5969,191 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Q1-2026 dividends payable</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="n">
-        <v>2001.79216</v>
+          <t>Export subsidy as a share of export revenue, FY2025 DISCLOSED rate</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>0.008556374712707386</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Q1-2026 finance costs</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="n">
-        <v>11.168843</v>
+          <t>Other income excluding the export subsidy, FY2025</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="n">
+        <v>20.696922</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>LENS INPUTS</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Q1-2026 dividends payable</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="n">
+        <v>2001.79216</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Replacement cost per annual tonne</t>
+          <t>Q1-2026 finance costs</t>
         </is>
       </c>
       <c r="B150" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
+        <v>11.168843</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Justified enterprise value per annual tonne</t>
-        </is>
-      </c>
-      <c r="B151" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
-      </c>
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>LENS INPUTS</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="F151" s="6" t="n"/>
+      <c r="G151" s="6" t="n"/>
+      <c r="H151" s="6" t="n"/>
+      <c r="I151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="n">
-        <v>4.5</v>
+          <t>Replacement cost per annual tonne</t>
+        </is>
+      </c>
+      <c r="B152" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="n">
-        <v>7</v>
+          <t>Justified enterprise value per annual tonne</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="n">
-        <v>0.312</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Normalised revenue haircut</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="n">
-        <v>0.9399999999999999</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Weight — cash-flow lens</t>
+          <t>Mid-cycle EBITDA margin</t>
         </is>
       </c>
       <c r="B156" s="9" t="n">
-        <v>0.5</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Weight — relative lens</t>
+          <t>Normalised revenue haircut</t>
         </is>
       </c>
       <c r="B157" s="9" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Weight — normalised lens</t>
+          <t>Weight — cash-flow lens</t>
         </is>
       </c>
       <c r="B158" s="9" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Weight — asset lens</t>
+          <t>Weight — relative lens</t>
         </is>
       </c>
       <c r="B159" s="9" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>SECTOR AND PEERS</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="n"/>
-      <c r="C160" s="6" t="n"/>
-      <c r="D160" s="6" t="n"/>
-      <c r="E160" s="6" t="n"/>
-      <c r="F160" s="6" t="n"/>
-      <c r="G160" s="6" t="n"/>
-      <c r="H160" s="6" t="n"/>
-      <c r="I160" s="6" t="n"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Weight — normalised lens</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Egyptian nameplate capacity</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
+          <t>Weight — asset lens</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Egyptian production 2025</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>SECTOR AND PEERS</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="6" t="n"/>
+      <c r="F162" s="6" t="n"/>
+      <c r="G162" s="6" t="n"/>
+      <c r="H162" s="6" t="n"/>
+      <c r="I162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Egyptian consumption 2025</t>
+          <t>Egyptian nameplate capacity</t>
         </is>
       </c>
       <c r="B163" s="12" t="n">
-        <v>53.9</v>
+        <v>76</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
@@ -6174,11 +6164,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Egyptian exports 2025</t>
+          <t>Egyptian production 2025</t>
         </is>
       </c>
       <c r="B164" s="12" t="n">
-        <v>18.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
@@ -6189,11 +6179,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dormant capacity under revival</t>
+          <t>Egyptian consumption 2025</t>
         </is>
       </c>
       <c r="B165" s="12" t="n">
-        <v>12.6</v>
+        <v>53.9</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
@@ -6204,72 +6194,102 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement revenue</t>
-        </is>
-      </c>
-      <c r="B166" s="15" t="n">
-        <v>9090</v>
+          <t>Egyptian exports 2025</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement profit</t>
-        </is>
-      </c>
-      <c r="B167" s="15" t="n">
-        <v>2290</v>
+          <t>Dormant capacity under revival</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement market capitalisation</t>
+          <t>Peer — Sinai Cement revenue</t>
         </is>
       </c>
       <c r="B168" s="15" t="n">
-        <v>20604.19</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef revenue</t>
+          <t>Peer — Sinai Cement profit</t>
         </is>
       </c>
       <c r="B169" s="15" t="n">
-        <v>5700</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef profit</t>
+          <t>Peer — Sinai Cement market capitalisation</t>
         </is>
       </c>
       <c r="B170" s="15" t="n">
-        <v>3946</v>
+        <v>20604.19</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>Peer — Misr Beni Suef revenue</t>
+        </is>
+      </c>
+      <c r="B171" s="15" t="n">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Peer — Misr Beni Suef profit</t>
+        </is>
+      </c>
+      <c r="B172" s="15" t="n">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B171" s="15" t="n">
+      <c r="B173" s="15" t="n">
         <v>13730</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>Every cell on this sheet is BLUE — an input. Nothing here is computed from anything else here.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>Everything on every other sheet that can be derived from these is a formula.</t>
         </is>
@@ -6277,8 +6297,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A173:J173"/>
-    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A175:J175"/>
+    <mergeCell ref="A176:J176"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8213,23 +8233,23 @@
         </is>
       </c>
       <c r="B9" s="26">
-        <f>B7-B8</f>
+        <f>B7-B8+Assumptions!$B$147*'Unit Build'!C60+Assumptions!$B$147*'Unit Build'!C61+Assumptions!$B$148*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>C7-C8</f>
+        <f>C7-C8+Assumptions!$B$147*'Unit Build'!D60+Assumptions!$B$147*'Unit Build'!D61+Assumptions!$B$148*Assumptions!$D$29</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>D7-D8</f>
+        <f>D7-D8+Assumptions!$B$147*'Unit Build'!E60+Assumptions!$B$147*'Unit Build'!E61+Assumptions!$B$148*Assumptions!$E$29</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>E7-E8</f>
+        <f>E7-E8+Assumptions!$B$147*'Unit Build'!F60+Assumptions!$B$147*'Unit Build'!F61+Assumptions!$B$148*Assumptions!$F$29</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>F7-F8</f>
+        <f>F7-F8+Assumptions!$B$147*'Unit Build'!G60+Assumptions!$B$147*'Unit Build'!G61+Assumptions!$B$148*Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
@@ -8524,7 +8544,7 @@
         </is>
       </c>
       <c r="B22" s="26">
-        <f>Assumptions!$B$13*Assumptions!$B$150*Assumptions!$B$11*Assumptions!$G$29</f>
+        <f>Assumptions!$B$13*Assumptions!$B$152*Assumptions!$B$11*Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
@@ -8790,12 +8810,12 @@
         <v/>
       </c>
       <c r="C41" s="32">
-        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03)+Assumptions!$B$122*(Assumptions!$B$43+0.0435)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
+        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03+Assumptions!$B$45)+Assumptions!$B$122*(Assumptions!$B$43+0.0435+Assumptions!$B$45)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
         <v/>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cost of debt, blended by currency</t>
+          <t>Cost of debt, blended by currency, POUND-EQUIVALENT</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9065,7 @@
         </is>
       </c>
       <c r="B62" s="30">
-        <f>Assumptions!$B$148*4/((C44+Assumptions!$B$138)/2)</f>
+        <f>Assumptions!$B$150*4/((C44+Assumptions!$B$138)/2)</f>
         <v/>
       </c>
     </row>
@@ -9578,23 +9598,23 @@
         <v/>
       </c>
       <c r="E11" s="24">
-        <f>E14-E13</f>
+        <f>E14-E13+Assumptions!$B$147*'Unit Build'!C60+Assumptions!$B$147*'Unit Build'!C61+Assumptions!$B$148*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="F11" s="24">
-        <f>F14-F13</f>
+        <f>F14-F13+Assumptions!$B$147*'Unit Build'!D60+Assumptions!$B$147*'Unit Build'!D61+Assumptions!$B$148*Assumptions!$D$29</f>
         <v/>
       </c>
       <c r="G11" s="24">
-        <f>G14-G13</f>
+        <f>G14-G13+Assumptions!$B$147*'Unit Build'!E60+Assumptions!$B$147*'Unit Build'!E61+Assumptions!$B$148*Assumptions!$E$29</f>
         <v/>
       </c>
       <c r="H11" s="24">
-        <f>H14-H13</f>
+        <f>H14-H13+Assumptions!$B$147*'Unit Build'!F60+Assumptions!$B$147*'Unit Build'!F61+Assumptions!$B$148*Assumptions!$F$29</f>
         <v/>
       </c>
       <c r="I11" s="24">
-        <f>I14-I13</f>
+        <f>I14-I13+Assumptions!$B$147*'Unit Build'!G60+Assumptions!$B$147*'Unit Build'!G61+Assumptions!$B$148*Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
